--- a/results/Int HRV.xlsx
+++ b/results/Int HRV.xlsx
@@ -878,52 +878,52 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.84 ± 3.22</t>
+          <t>57.76 ± 3.51</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>58.41 ± 3.36</t>
+          <t>58.36 ± 3.64</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>58.13 ± 3.23</t>
+          <t>58.02 ± 3.56</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>61.57 ± 4.44</t>
+          <t>61.58 ± 4.56</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.00 ± 5.49</t>
+          <t>63.19 ± 5.58</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15.80 ± 6.55</t>
+          <t>15.64 ± 7.13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>63.06 ± 5.47</t>
+          <t>63.25 ± 5.56</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>42.25 ± 3.05</t>
+          <t>42.41 ± 3.26</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>16.21 ± 7.99</t>
+          <t>16.25 ± 8.07</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>10.39 ± 6.44</t>
+          <t>10.42 ± 6.31</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1310,52 +1310,52 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>57.98 ± 3.22</t>
+          <t>58.06 ± 3.12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>58.59 ± 3.38</t>
+          <t>58.67 ± 3.27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>58.26 ± 3.30</t>
+          <t>58.34 ± 3.14</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>61.73 ± 4.39</t>
+          <t>61.64 ± 4.18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>63.17 ± 5.74</t>
+          <t>62.90 ± 5.51</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>16.09 ± 6.54</t>
+          <t>16.25 ± 6.36</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>63.21 ± 5.75</t>
+          <t>62.98 ± 5.49</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>42.02 ± 3.10</t>
+          <t>42.27 ± 2.81</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>15.91 ± 8.09</t>
+          <t>15.98 ± 8.14</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>10.05 ± 6.36</t>
+          <t>10.02 ± 6.58</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1742,52 +1742,52 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>57.93 ± 3.67</t>
+          <t>58.00 ± 3.15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>58.52 ± 3.86</t>
+          <t>58.56 ± 3.32</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>58.20 ± 3.75</t>
+          <t>58.27 ± 3.22</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>61.52 ± 4.40</t>
+          <t>61.63 ± 4.29</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>63.10 ± 5.50</t>
+          <t>63.07 ± 5.58</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>15.99 ± 7.46</t>
+          <t>16.11 ± 6.42</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>63.16 ± 5.46</t>
+          <t>63.10 ± 5.55</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>42.33 ± 3.44</t>
+          <t>42.50 ± 2.84</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>16.16 ± 7.92</t>
+          <t>15.95 ± 7.97</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>10.03 ± 6.38</t>
+          <t>10.45 ± 6.12</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2174,52 +2174,52 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>57.82 ± 3.29</t>
+          <t>57.70 ± 3.30</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>58.40 ± 3.47</t>
+          <t>58.29 ± 3.45</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>58.08 ± 3.38</t>
+          <t>57.96 ± 3.38</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>61.48 ± 4.41</t>
+          <t>61.30 ± 4.51</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>63.09 ± 5.55</t>
+          <t>62.75 ± 5.58</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>15.76 ± 6.68</t>
+          <t>15.52 ± 6.72</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>63.16 ± 5.53</t>
+          <t>62.84 ± 5.57</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>42.48 ± 3.23</t>
+          <t>42.63 ± 3.17</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>16.07 ± 7.68</t>
+          <t>15.65 ± 7.66</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>10.45 ± 5.90</t>
+          <t>9.92 ± 6.11</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2606,52 +2606,52 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>57.78 ± 3.51</t>
+          <t>57.50 ± 3.18</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>58.38 ± 3.65</t>
+          <t>58.07 ± 3.30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>58.05 ± 3.56</t>
+          <t>57.76 ± 3.23</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>61.32 ± 4.58</t>
+          <t>61.43 ± 4.27</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>62.87 ± 5.70</t>
+          <t>62.96 ± 5.71</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>15.68 ± 7.12</t>
+          <t>15.10 ± 6.45</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>62.89 ± 5.71</t>
+          <t>63.04 ± 5.69</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>42.65 ± 3.04</t>
+          <t>42.47 ± 3.15</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>16.09 ± 8.45</t>
+          <t>16.24 ± 8.66</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>9.98 ± 6.43</t>
+          <t>10.22 ± 6.48</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -3038,52 +3038,52 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>59.56 ± 5.06</t>
+          <t>59.91 ± 5.38</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>59.92 ± 4.86</t>
+          <t>60.27 ± 5.16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>59.43 ± 5.15</t>
+          <t>59.74 ± 5.46</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>63.80 ± 6.64</t>
+          <t>63.81 ± 6.47</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>64.29 ± 7.32</t>
+          <t>64.28 ± 7.41</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>19.13 ± 10.05</t>
+          <t>19.81 ± 10.65</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>64.26 ± 7.30</t>
+          <t>64.30 ± 7.40</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>40.54 ± 5.01</t>
+          <t>40.23 ± 5.06</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>17.44 ± 9.62</t>
+          <t>17.25 ± 10.05</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>11.61 ± 8.41</t>
+          <t>10.87 ± 8.86</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -3470,52 +3470,52 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>60.91 ± 3.47</t>
+          <t>61.17 ± 3.13</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.36 ± 3.61</t>
+          <t>61.61 ± 3.25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>60.99 ± 3.63</t>
+          <t>61.28 ± 3.26</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>65.50 ± 4.66</t>
+          <t>65.41 ± 4.68</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>65.48 ± 5.87</t>
+          <t>65.37 ± 5.60</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>21.94 ± 6.99</t>
+          <t>22.47 ± 6.33</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>65.53 ± 5.79</t>
+          <t>65.42 ± 5.52</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>39.42 ± 3.58</t>
+          <t>39.25 ± 3.56</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>20.18 ± 8.80</t>
+          <t>19.41 ± 8.18</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>12.80 ± 7.24</t>
+          <t>12.82 ± 6.52</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3902,52 +3902,52 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>59.55 ± 4.08</t>
+          <t>59.34 ± 3.96</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>59.62 ± 4.04</t>
+          <t>59.42 ± 3.91</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>59.45 ± 4.04</t>
+          <t>59.25 ± 3.90</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>63.52 ± 6.14</t>
+          <t>63.37 ± 6.12</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>62.11 ± 7.01</t>
+          <t>62.17 ± 7.03</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>19.09 ± 8.16</t>
+          <t>18.67 ± 7.91</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>62.14 ± 7.06</t>
+          <t>62.20 ± 7.08</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>40.72 ± 4.20</t>
+          <t>41.03 ± 4.26</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>18.14 ± 11.32</t>
+          <t>18.11 ± 11.58</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>10.89 ± 9.73</t>
+          <t>11.17 ± 9.80</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -4334,52 +4334,52 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>59.04 ± 6.62</t>
+          <t>58.54 ± 6.48</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>59.00 ± 6.50</t>
+          <t>58.51 ± 6.35</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>58.74 ± 6.78</t>
+          <t>58.25 ± 6.62</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>62.78 ± 9.19</t>
+          <t>62.97 ± 9.28</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>62.14 ± 9.01</t>
+          <t>62.38 ± 9.02</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>18.01 ± 13.18</t>
+          <t>17.01 ± 12.88</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>62.18 ± 8.97</t>
+          <t>62.41 ± 8.97</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>41.19 ± 6.78</t>
+          <t>41.40 ± 6.89</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>20.19 ± 10.57</t>
+          <t>21.15 ± 9.88</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>12.34 ± 5.91</t>
+          <t>12.81 ± 6.57</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4766,52 +4766,52 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>59.32 ± 5.04</t>
+          <t>59.31 ± 4.86</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>59.58 ± 4.87</t>
+          <t>59.53 ± 4.79</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>59.24 ± 5.00</t>
+          <t>59.21 ± 4.89</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>64.09 ± 7.73</t>
+          <t>64.10 ± 7.79</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>59.62 ± 10.10</t>
+          <t>59.53 ± 10.00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>18.62 ± 10.00</t>
+          <t>18.61 ± 9.66</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>59.64 ± 10.06</t>
+          <t>59.56 ± 9.94</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>39.70 ± 5.06</t>
+          <t>39.82 ± 4.88</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>18.45 ± 10.77</t>
+          <t>17.94 ± 10.13</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>11.59 ± 8.47</t>
+          <t>10.97 ± 7.81</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -5198,52 +5198,52 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>58.11 ± 6.16</t>
+          <t>58.50 ± 6.22</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>58.04 ± 6.09</t>
+          <t>58.43 ± 6.14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>57.90 ± 6.19</t>
+          <t>58.29 ± 6.23</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>62.90 ± 8.36</t>
+          <t>63.12 ± 8.22</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>59.08 ± 9.04</t>
+          <t>59.19 ± 8.90</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>16.12 ± 12.26</t>
+          <t>16.90 ± 12.37</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>59.09 ± 8.96</t>
+          <t>59.23 ± 8.81</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>41.57 ± 5.75</t>
+          <t>41.22 ± 5.92</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>18.91 ± 8.85</t>
+          <t>18.91 ± 8.73</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>12.30 ± 5.94</t>
+          <t>11.72 ± 5.48</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -5630,52 +5630,52 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>57.44 ± 5.32</t>
+          <t>57.56 ± 4.98</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>58.76 ± 5.33</t>
+          <t>58.91 ± 5.00</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>58.38 ± 5.20</t>
+          <t>58.54 ± 4.82</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>64.33 ± 8.03</t>
+          <t>64.59 ± 7.83</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>53.19 ± 9.03</t>
+          <t>53.80 ± 8.99</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>14.97 ± 10.57</t>
+          <t>15.21 ± 9.89</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>53.19 ± 9.07</t>
+          <t>53.78 ± 9.02</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>40.41 ± 5.61</t>
+          <t>40.20 ± 5.47</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>17.41 ± 7.99</t>
+          <t>17.90 ± 8.44</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>10.96 ± 5.70</t>
+          <t>11.85 ± 6.25</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -6062,52 +6062,52 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>56.42 ± 4.75</t>
+          <t>56.21 ± 4.74</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>58.91 ± 4.60</t>
+          <t>58.80 ± 4.54</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>58.34 ± 4.56</t>
+          <t>58.19 ± 4.60</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>64.28 ± 7.02</t>
+          <t>64.01 ± 7.04</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>48.51 ± 7.32</t>
+          <t>48.61 ± 7.53</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>12.76 ± 9.64</t>
+          <t>12.34 ± 9.64</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>48.60 ± 7.24</t>
+          <t>48.61 ± 7.54</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>40.61 ± 4.92</t>
+          <t>41.07 ± 5.20</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>16.26 ± 7.28</t>
+          <t>15.97 ± 7.14</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>10.30 ± 5.63</t>
+          <t>10.43 ± 5.87</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -6494,52 +6494,52 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>55.33 ± 5.62</t>
+          <t>55.07 ± 6.19</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>59.16 ± 5.58</t>
+          <t>58.98 ± 5.99</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>58.48 ± 5.59</t>
+          <t>58.26 ± 6.01</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>62.42 ± 10.58</t>
+          <t>62.64 ± 10.47</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>46.28 ± 10.40</t>
+          <t>46.06 ± 10.24</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>10.70 ± 11.09</t>
+          <t>10.16 ± 12.26</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>46.21 ± 10.40</t>
+          <t>45.99 ± 10.24</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>41.56 ± 6.85</t>
+          <t>41.08 ± 6.61</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>15.23 ± 10.79</t>
+          <t>15.50 ± 10.88</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>8.28 ± 6.59</t>
+          <t>8.10 ± 6.66</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -6926,52 +6926,52 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>56.65 ± 6.92</t>
+          <t>56.59 ± 6.58</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>64.81 ± 6.33</t>
+          <t>64.80 ± 6.21</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>63.26 ± 5.79</t>
+          <t>63.27 ± 5.56</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>66.57 ± 9.64</t>
+          <t>66.44 ± 9.69</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>45.36 ± 13.88</t>
+          <t>45.24 ± 13.50</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>14.06 ± 14.56</t>
+          <t>14.02 ± 13.95</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>45.32 ± 13.87</t>
+          <t>45.19 ± 13.50</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>37.07 ± 7.27</t>
+          <t>37.49 ± 7.25</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>19.91 ± 15.28</t>
+          <t>20.72 ± 15.92</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>10.54 ± 11.21</t>
+          <t>10.75 ± 10.82</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -7358,52 +7358,52 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>54.76 ± 8.16</t>
+          <t>54.02 ± 8.37</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>68.38 ± 6.56</t>
+          <t>67.84 ± 6.53</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>66.07 ± 6.02</t>
+          <t>65.40 ± 6.30</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>63.88 ± 11.03</t>
+          <t>63.69 ± 11.25</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>39.87 ± 14.50</t>
+          <t>39.58 ± 14.79</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>10.10 ± 16.20</t>
+          <t>8.29 ± 17.02</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>39.80 ± 14.51</t>
+          <t>39.50 ± 14.79</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>39.11 ± 8.29</t>
+          <t>38.94 ± 8.08</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>19.14 ± 16.56</t>
+          <t>17.83 ± 16.96</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>12.57 ± 15.19</t>
+          <t>11.94 ± 15.03</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -7790,52 +7790,52 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>52.75 ± 4.98</t>
+          <t>52.52 ± 4.74</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>71.16 ± 4.78</t>
+          <t>71.16 ± 4.72</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>68.16 ± 4.19</t>
+          <t>68.05 ± 4.23</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>59.76 ± 10.07</t>
+          <t>59.49 ± 10.49</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>31.90 ± 11.69</t>
+          <t>31.72 ± 12.01</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>5.80 ± 11.15</t>
+          <t>5.36 ± 11.11</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>31.70 ± 11.65</t>
+          <t>31.54 ± 11.98</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>43.14 ± 6.52</t>
+          <t>42.84 ± 7.28</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>16.23 ± 12.44</t>
+          <t>16.41 ± 12.28</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>10.82 ± 9.30</t>
+          <t>10.34 ± 9.24</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -8222,52 +8222,52 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>53.03 ± 8.55</t>
+          <t>52.88 ± 8.60</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>76.28 ± 7.65</t>
+          <t>76.11 ± 7.45</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>73.73 ± 7.20</t>
+          <t>73.63 ± 6.88</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>61.15 ± 15.52</t>
+          <t>61.29 ± 15.84</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>31.53 ± 16.62</t>
+          <t>31.15 ± 16.63</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>7.29 ± 18.62</t>
+          <t>6.68 ± 18.83</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>31.44 ± 16.62</t>
+          <t>31.06 ± 16.64</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>43.23 ± 11.17</t>
+          <t>42.80 ± 10.91</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>20.40 ± 15.48</t>
+          <t>19.32 ± 14.86</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>14.03 ± 13.58</t>
+          <t>13.40 ± 14.24</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -8654,52 +8654,52 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>53.83 ± 6.69</t>
+          <t>53.78 ± 6.53</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>78.09 ± 5.86</t>
+          <t>77.96 ± 5.85</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>75.22 ± 5.97</t>
+          <t>75.15 ± 5.88</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>61.32 ± 9.77</t>
+          <t>61.16 ± 9.38</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>28.86 ± 14.65</t>
+          <t>28.46 ± 14.12</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>8.29 ± 15.51</t>
+          <t>8.12 ± 15.01</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>28.77 ± 14.66</t>
+          <t>28.36 ± 14.13</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>41.98 ± 7.03</t>
+          <t>42.62 ± 7.20</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>17.15 ± 14.47</t>
+          <t>17.06 ± 13.95</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>11.85 ± 13.95</t>
+          <t>11.39 ± 13.39</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -9086,52 +9086,52 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>53.54 ± 8.94</t>
+          <t>53.74 ± 8.97</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>79.85 ± 6.49</t>
+          <t>79.96 ± 6.58</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>77.55 ± 6.41</t>
+          <t>77.69 ± 6.50</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>61.90 ± 13.83</t>
+          <t>62.08 ± 13.39</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>28.99 ± 15.47</t>
+          <t>28.89 ± 15.64</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>8.45 ± 20.73</t>
+          <t>8.92 ± 20.95</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>28.90 ± 15.48</t>
+          <t>28.80 ± 15.68</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>41.27 ± 8.49</t>
+          <t>41.43 ± 8.53</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>19.14 ± 16.35</t>
+          <t>19.39 ± 16.14</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>13.84 ± 15.78</t>
+          <t>14.29 ± 15.57</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -9518,52 +9518,52 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>59.14 ± 13.34</t>
+          <t>59.18 ± 13.44</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>83.11 ± 4.59</t>
+          <t>83.22 ± 4.49</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>81.03 ± 6.77</t>
+          <t>81.08 ± 6.79</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>62.50 ± 8.02</t>
+          <t>61.89 ± 8.39</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>27.09 ± 16.91</t>
+          <t>26.17 ± 16.40</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>11.45 ± 19.55</t>
+          <t>11.42 ± 19.33</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>31.94 ± 15.45</t>
+          <t>31.06 ± 15.22</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>47.69 ± 18.02</t>
+          <t>48.73 ± 17.86</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>22.43 ± 18.30</t>
+          <t>22.75 ± 18.43</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>17.42 ± 18.36</t>
+          <t>17.10 ± 18.19</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
